--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 14 Jobs.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
